--- a/Data/2024 Data/Results.xlsx
+++ b/Data/2024 Data/Results.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27830"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BGC Show\Garden-Show\Data\2024 Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC596CC5-EE91-4ED4-90BD-E39810D6FF4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2544" yWindow="2220" windowWidth="17376" windowHeight="9012" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Award List" sheetId="1" r:id="rId1"/>
     <sheet name="Class Results" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="225">
   <si>
     <t>Trophies</t>
   </si>
@@ -164,10 +158,10 @@
     <t>Most points by a Young Gardener in Sections Q, R &amp; S</t>
   </si>
   <si>
-    <t>River Munro</t>
-  </si>
-  <si>
-    <t>6 points</t>
+    <t>Graeson Dunn</t>
+  </si>
+  <si>
+    <t>9 points</t>
   </si>
   <si>
     <t>Jeanette MacDonald Shield</t>
@@ -194,6 +188,9 @@
     <t>Best in section L</t>
   </si>
   <si>
+    <t>Lemon curd</t>
+  </si>
+  <si>
     <t>Best in section M</t>
   </si>
   <si>
@@ -693,22 +690,13 @@
   </si>
   <si>
     <t>S: YOUNG GARDENERS (Primary 6 &amp; 7)</t>
-  </si>
-  <si>
-    <t>Eric and Lynda Dodd</t>
-  </si>
-  <si>
-    <t>5 points</t>
-  </si>
-  <si>
-    <t>Lemon curd</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -759,21 +747,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -811,7 +791,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -845,7 +825,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -880,10 +859,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1056,16 +1034,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="44.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="44.7109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1079,7 +1057,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1093,7 +1071,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -1104,7 +1082,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -1115,7 +1093,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1129,7 +1107,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1140,7 +1118,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -1151,7 +1129,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
@@ -1162,7 +1140,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
@@ -1173,7 +1151,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -1184,7 +1162,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -1195,7 +1173,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
@@ -1206,7 +1184,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>34</v>
       </c>
@@ -1217,7 +1195,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
@@ -1231,7 +1209,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>41</v>
       </c>
@@ -1239,13 +1217,13 @@
         <v>38</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>224</v>
+        <v>39</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -1259,7 +1237,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>45</v>
       </c>
@@ -1273,7 +1251,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>49</v>
       </c>
@@ -1287,7 +1265,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>52</v>
       </c>
@@ -1301,12 +1279,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="A20" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="B21" s="1" t="s">
         <v>56</v>
       </c>
@@ -1314,18 +1292,18 @@
         <v>6</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="B23" s="1" t="s">
         <v>38</v>
       </c>
@@ -1336,7 +1314,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="B24" s="1" t="s">
         <v>43</v>
       </c>
@@ -1347,9 +1325,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="B25" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>39</v>
@@ -1358,9 +1336,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="B26" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>36</v>
@@ -1369,1117 +1347,1117 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:4" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="B27" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
   <printOptions gridLines="1"/>
-  <pageMargins left="0.43307086614173229" right="0.43307086614173229" top="0.35433070866141736" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D96"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40.6640625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="25.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="40.7109375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="25.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="D8" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
+      <c r="A37" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
+      <c r="A41" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
+      <c r="A47" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
+      <c r="A51" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
+      <c r="A53" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
+      <c r="A56" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="D65" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
+      <c r="A67" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
+      <c r="A82" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
+      <c r="A86" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="A89" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
       <c r="A90" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
       <c r="A91" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="A92" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
       <c r="A93" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
       <c r="A94" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:4">
       <c r="A95" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="A96" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
